--- a/E/EG1A.xlsx
+++ b/E/EG1A.xlsx
@@ -11,114 +11,120 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="198" uniqueCount="83">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="186" uniqueCount="80">
   <si>
     <t/>
   </si>
   <si>
+    <t>20101825</t>
+  </si>
+  <si>
+    <t>VDRAN XMRT1+ MDU 900</t>
+  </si>
+  <si>
+    <t>EG1A</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>RT,(E-2B)</t>
+  </si>
+  <si>
     <t>20142950</t>
   </si>
   <si>
     <t>BEBELAC 1+ VAN 775G</t>
   </si>
   <si>
-    <t>EG1A</t>
-  </si>
-  <si>
-    <t>1</t>
-  </si>
-  <si>
     <t>2</t>
   </si>
   <si>
     <t>RT,(E-1B)</t>
   </si>
   <si>
-    <t>20131625</t>
-  </si>
-  <si>
-    <t>LARISST FCL.TIS 250S</t>
+    <t>20114021</t>
+  </si>
+  <si>
+    <t>IDM TISU WJH PRM 100</t>
   </si>
   <si>
     <t>3</t>
   </si>
   <si>
-    <t>PT,(E-4B)</t>
-  </si>
-  <si>
-    <t>20077369</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF BLUBR 15</t>
-  </si>
-  <si>
-    <t>20092042</t>
-  </si>
-  <si>
-    <t>PRMINA PUFF STRWAP15</t>
-  </si>
-  <si>
-    <t>20139421</t>
-  </si>
-  <si>
-    <t>PRMINA YGR MLT SRW 8</t>
-  </si>
-  <si>
-    <t>20142943</t>
-  </si>
-  <si>
-    <t>IDM CHOCO CRACKR 100</t>
+    <t>PT</t>
+  </si>
+  <si>
+    <t>20141464</t>
+  </si>
+  <si>
+    <t>RMN YES HKTA CHKN88G</t>
   </si>
   <si>
     <t>4</t>
   </si>
   <si>
-    <t>20117684</t>
-  </si>
-  <si>
-    <t>KALPA SHRE IT 90G</t>
+    <t>20141466</t>
+  </si>
+  <si>
+    <t>RMN YES TKYO CHKN84G</t>
   </si>
   <si>
     <t>5</t>
   </si>
   <si>
-    <t>20002504</t>
-  </si>
-  <si>
-    <t>ADEM SARI BOX 5'S</t>
+    <t>20061938</t>
+  </si>
+  <si>
+    <t>SUPER O2 SPRTVO 600</t>
+  </si>
+  <si>
+    <t>20139699</t>
+  </si>
+  <si>
+    <t>OASIS  MNRL PH9 500</t>
+  </si>
+  <si>
+    <t>20053867</t>
+  </si>
+  <si>
+    <t>TEH GELAS BTL 350ML</t>
+  </si>
+  <si>
+    <t>20136193</t>
+  </si>
+  <si>
+    <t>SO GOOD SUSU STRL189</t>
+  </si>
+  <si>
+    <t>20038425</t>
+  </si>
+  <si>
+    <t>NTRIVE/B BLCKRNT 100</t>
+  </si>
+  <si>
+    <t>RT,(E-14H)</t>
+  </si>
+  <si>
+    <t>20071510</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL LYCH 100</t>
   </si>
   <si>
     <t>6</t>
   </si>
   <si>
-    <t>20103368</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LMN 330</t>
-  </si>
-  <si>
-    <t>RT,(E-2B)</t>
-  </si>
-  <si>
-    <t>20103178</t>
-  </si>
-  <si>
-    <t>HMVTON C1000 LSO 330</t>
-  </si>
-  <si>
-    <t>20071510</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL LYCH 100</t>
-  </si>
-  <si>
-    <t>RT,(E-14H)</t>
-  </si>
-  <si>
-    <t>20038425</t>
-  </si>
-  <si>
-    <t>NTRIVE/B BLCKRNT 100</t>
+    <t>20082247</t>
+  </si>
+  <si>
+    <t>NTRVE BNCOL ORG 100</t>
+  </si>
+  <si>
+    <t>7</t>
+  </si>
+  <si>
+    <t>RT,(E-0.5B)</t>
   </si>
   <si>
     <t>20055226</t>
@@ -127,139 +133,124 @@
     <t>NTRIVE/B  STRWBRY100</t>
   </si>
   <si>
-    <t>20082247</t>
-  </si>
-  <si>
-    <t>NTRVE BNCOL ORG 100</t>
-  </si>
-  <si>
-    <t>RT,(E-0.5B)</t>
-  </si>
-  <si>
-    <t>20139596</t>
-  </si>
-  <si>
-    <t>PPSODNT SENSI EXP 60</t>
-  </si>
-  <si>
-    <t>7</t>
+    <t>8</t>
+  </si>
+  <si>
+    <t>20143287</t>
+  </si>
+  <si>
+    <t>JYO KOR SWD ORI 4.8</t>
+  </si>
+  <si>
+    <t>RT,(E-27H)</t>
+  </si>
+  <si>
+    <t>20034686</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW UBI 100</t>
+  </si>
+  <si>
+    <t>20034685</t>
+  </si>
+  <si>
+    <t>OISHI PILLOW CHO 100</t>
+  </si>
+  <si>
+    <t>20134686</t>
+  </si>
+  <si>
+    <t>IDM KCG PISTACHIO 55</t>
   </si>
   <si>
     <t>PT,(E-1B)</t>
   </si>
   <si>
-    <t>20143275</t>
-  </si>
-  <si>
-    <t>PPSDNT PRCRE MPRTC90</t>
-  </si>
-  <si>
-    <t>9</t>
-  </si>
-  <si>
-    <t>20143276</t>
-  </si>
-  <si>
-    <t>PPSDNT PRCRE ICFRS90</t>
-  </si>
-  <si>
-    <t>10</t>
-  </si>
-  <si>
-    <t>20117687</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA MTCHA 240</t>
+    <t>10003844</t>
+  </si>
+  <si>
+    <t>INACO JELLY MNI 15'S</t>
+  </si>
+  <si>
+    <t>20028585</t>
+  </si>
+  <si>
+    <t>MI GEMEZ ENAK PREM22</t>
+  </si>
+  <si>
+    <t>20143712</t>
+  </si>
+  <si>
+    <t>ANTANGIN GNIGHT BOX</t>
+  </si>
+  <si>
+    <t>RT,(E-4B)</t>
+  </si>
+  <si>
+    <t>20041562</t>
+  </si>
+  <si>
+    <t>TOP COFFEE SUSU 10'S</t>
+  </si>
+  <si>
+    <t>20143150</t>
+  </si>
+  <si>
+    <t>MAYA TN MYK KDL185G</t>
+  </si>
+  <si>
+    <t>20111592</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSNT BRIES</t>
+  </si>
+  <si>
+    <t>20115438</t>
+  </si>
+  <si>
+    <t>5DAYS CROISSANT CHSE</t>
+  </si>
+  <si>
+    <t>20136661</t>
+  </si>
+  <si>
+    <t>5 DAYS CHOCO BANANA</t>
+  </si>
+  <si>
+    <t>20140418</t>
+  </si>
+  <si>
+    <t>SOFTX GRVTY 23CM 20S</t>
+  </si>
+  <si>
+    <t>RT</t>
+  </si>
+  <si>
+    <t>20141938</t>
+  </si>
+  <si>
+    <t>G2G MCL WTR BRIGH130</t>
   </si>
   <si>
     <t>RT,(E-3B)</t>
   </si>
   <si>
-    <t>20117682</t>
-  </si>
-  <si>
-    <t>DLMNT BOBA RD.VEL240</t>
-  </si>
-  <si>
-    <t>20121662</t>
-  </si>
-  <si>
-    <t>INDOMLK KD LS CKL115</t>
-  </si>
-  <si>
-    <t>20088789</t>
-  </si>
-  <si>
-    <t>INDOMLK KID F.CRM115</t>
-  </si>
-  <si>
-    <t>20134673</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT PLN 6X110</t>
-  </si>
-  <si>
-    <t>20083795</t>
-  </si>
-  <si>
-    <t>F/FLAG UHT CHO 6X110</t>
-  </si>
-  <si>
-    <t>10036647</t>
-  </si>
-  <si>
-    <t>ULTRA SUSU UHT CHO1L</t>
-  </si>
-  <si>
-    <t>10004669</t>
-  </si>
-  <si>
-    <t>ULTRA UHT CHOCO 250M</t>
-  </si>
-  <si>
-    <t>10004668</t>
-  </si>
-  <si>
-    <t>ULTRA UHT STRAW 250M</t>
-  </si>
-  <si>
-    <t>20037974</t>
-  </si>
-  <si>
-    <t>ULTRA UHT MOKA 250</t>
-  </si>
-  <si>
-    <t>20134390</t>
-  </si>
-  <si>
-    <t>CIMORY BBS LKTSA 250</t>
-  </si>
-  <si>
-    <t>20140793</t>
-  </si>
-  <si>
-    <t>CIMORY UHT MTCHA 225</t>
-  </si>
-  <si>
-    <t>20138050</t>
-  </si>
-  <si>
-    <t>MUJIGAE WTRMLN 250</t>
-  </si>
-  <si>
-    <t>20110968</t>
-  </si>
-  <si>
-    <t>MUJIGAE BNNA MLK 250</t>
-  </si>
-  <si>
-    <t>8</t>
-  </si>
-  <si>
-    <t>20142466</t>
-  </si>
-  <si>
-    <t>BEBELAC STRAW 105</t>
+    <t>20141073</t>
+  </si>
+  <si>
+    <t>G2G MC WTR BLUBR 130</t>
+  </si>
+  <si>
+    <t>20131332</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F SKR LMI10</t>
+  </si>
+  <si>
+    <t>20131331</t>
+  </si>
+  <si>
+    <t>AIRPRO A/F CLWV TD10</t>
   </si>
 </sst>
 </file>
@@ -652,14 +643,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:F33"/>
+  <dimension ref="A1:F31"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="10" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="3" customWidth="1"/>
-    <col min="5" max="5" width="4" customWidth="1"/>
+    <col min="4" max="5" width="3" customWidth="1"/>
     <col min="6" max="6" width="13" customWidth="1"/>
   </cols>
   <sheetData>
@@ -697,18 +687,18 @@
         <v>4</v>
       </c>
       <c r="E2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>5</v>
-      </c>
-      <c r="F2" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="1" t="s">
         <v>7</v>
-      </c>
-      <c r="B3" s="1" t="s">
-        <v>8</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>3</v>
@@ -717,130 +707,130 @@
         <v>4</v>
       </c>
       <c r="E3" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F3" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F3" s="1" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="B4" s="1" t="s">
+      <c r="C4" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D4" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="E4" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F4" s="1" t="s">
-        <v>6</v>
+        <v>13</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="C5" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E5" s="1" t="s">
-        <v>5</v>
+        <v>16</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="B6" s="1" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C6" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E6" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F6" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="B7" s="1" t="s">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="C7" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E7" s="1" t="s">
-        <v>19</v>
+        <v>4</v>
       </c>
       <c r="F7" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="1" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B8" s="1" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E8" s="1" t="s">
-        <v>22</v>
+        <v>8</v>
       </c>
       <c r="F8" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="C9" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="E9" s="1" t="s">
-        <v>25</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
@@ -854,33 +844,33 @@
         <v>3</v>
       </c>
       <c r="D10" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E10" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F10" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E10" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="B11" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="B11" s="1" t="s">
+      <c r="C11" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D11" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="E11" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="F11" s="1" t="s">
         <v>30</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="E11" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.25">
@@ -894,13 +884,13 @@
         <v>3</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E12" s="1" t="s">
-        <v>9</v>
+        <v>33</v>
       </c>
       <c r="F12" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.25">
@@ -914,93 +904,93 @@
         <v>3</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E13" s="1" t="s">
-        <v>19</v>
+        <v>36</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>33</v>
+        <v>37</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="1" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E14" s="1" t="s">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="F14" s="1" t="s">
-        <v>33</v>
+        <v>30</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A15" s="1" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>25</v>
+        <v>4</v>
       </c>
       <c r="F15" s="1" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="1" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C16" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D16" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E16" s="1" t="s">
+        <v>8</v>
+      </c>
+      <c r="F16" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E16" s="1" t="s">
-        <v>43</v>
-      </c>
-      <c r="F16" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="1" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E17" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17" s="1" t="s">
         <v>9</v>
-      </c>
-      <c r="E17" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F17" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.25">
@@ -1014,13 +1004,13 @@
         <v>3</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="E18" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="F18" s="1" t="s">
         <v>50</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.25">
@@ -1034,53 +1024,53 @@
         <v>3</v>
       </c>
       <c r="D19" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E19" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="E19" s="1" t="s">
-        <v>4</v>
-      </c>
       <c r="F19" s="1" t="s">
-        <v>53</v>
+        <v>5</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="1" t="s">
+        <v>53</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="B20" s="1" t="s">
-        <v>55</v>
-      </c>
       <c r="C20" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>19</v>
+        <v>12</v>
       </c>
       <c r="E20" s="1" t="s">
-        <v>5</v>
+        <v>33</v>
       </c>
       <c r="F20" s="1" t="s">
-        <v>53</v>
+        <v>9</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A21" s="1" t="s">
+        <v>55</v>
+      </c>
+      <c r="B21" s="1" t="s">
         <v>56</v>
       </c>
-      <c r="B21" s="1" t="s">
+      <c r="C21" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="E21" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="F21" s="1" t="s">
         <v>57</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="E21" s="1" t="s">
-        <v>19</v>
-      </c>
-      <c r="F21" s="1" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.25">
@@ -1094,13 +1084,13 @@
         <v>3</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E22" s="1" t="s">
-        <v>22</v>
+        <v>4</v>
       </c>
       <c r="F22" s="1" t="s">
-        <v>6</v>
+        <v>57</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.25">
@@ -1114,13 +1104,13 @@
         <v>3</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E23" s="1" t="s">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="F23" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.25">
@@ -1134,13 +1124,13 @@
         <v>3</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="E24" s="1" t="s">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="F24" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.25">
@@ -1154,13 +1144,13 @@
         <v>3</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E25" s="1" t="s">
-        <v>4</v>
+        <v>16</v>
       </c>
       <c r="F25" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.25">
@@ -1174,13 +1164,13 @@
         <v>3</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>22</v>
+        <v>16</v>
       </c>
       <c r="E26" s="1" t="s">
-        <v>5</v>
+        <v>19</v>
       </c>
       <c r="F26" s="1" t="s">
-        <v>6</v>
+        <v>37</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.25">
@@ -1194,133 +1184,93 @@
         <v>3</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E27" s="1" t="s">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="F27" s="1" t="s">
-        <v>6</v>
+        <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A28" s="1" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="B28" s="1" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C28" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E28" s="1" t="s">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="F28" s="1" t="s">
-        <v>6</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A29" s="1" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="B29" s="1" t="s">
+        <v>75</v>
+      </c>
+      <c r="C29" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>19</v>
+      </c>
+      <c r="E29" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29" s="1" t="s">
         <v>73</v>
-      </c>
-      <c r="C29" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E29" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="F29" s="1" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A30" s="1" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C30" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E30" s="1" t="s">
-        <v>25</v>
+        <v>19</v>
       </c>
       <c r="F30" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A31" s="1" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="B31" s="1" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C31" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="E31" s="1" t="s">
-        <v>43</v>
+        <v>33</v>
       </c>
       <c r="F31" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="32" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A32" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="B32" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C32" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D32" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E32" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="F32" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="33" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A33" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="B33" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C33" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="E33" s="1" t="s">
-        <v>47</v>
-      </c>
-      <c r="F33" s="1" t="s">
-        <v>6</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
